--- a/artfynd/A 13971-2023 artfynd.xlsx
+++ b/artfynd/A 13971-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13971-2023 artfynd.xlsx
+++ b/artfynd/A 13971-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86747093</v>
+        <v>86747092</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>219793</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mossnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Dactylorhiza majalis subsp. sphagnicola</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Höppner) H. A. Pedersen &amp; Hedrén</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
@@ -716,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556704.7006726186</v>
+        <v>556733</v>
       </c>
       <c r="R2" t="n">
-        <v>6627565.984569392</v>
+        <v>6627518</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,19 +748,9 @@
           <t>2020-07-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,6 +779,218 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>94735516</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99056</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219793</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mossnycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza majalis subsp. sphagnicola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Höppner) H. A. Pedersen &amp; Hedrén</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>556734</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6627516</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-07-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-07-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Grabs</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Grabs</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>86747093</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ljusvattnet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>556705</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6627566</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-07-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-07-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Myr, mestadels öppen</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bengt Stridh, Tom Sävström, Lars Woxberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13971-2023 artfynd.xlsx
+++ b/artfynd/A 13971-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86747092</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94735516</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,8 +1006,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86747093</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>